--- a/events/Penrith_2025_WCH/Penrith_2025_WCH_start.xlsx
+++ b/events/Penrith_2025_WCH/Penrith_2025_WCH_start.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13:20:00</t>
+          <t>13:20:02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>13:23:00</t>
+          <t>13:23:01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>13:33:00</t>
+          <t>13:33:02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>13:34:00</t>
+          <t>13:33:59</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13:38:00</t>
+          <t>13:37:59</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13:39:00</t>
+          <t>13:39:01</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>13:40:00</t>
+          <t>13:40:01</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>13:42:00</t>
+          <t>13:42:03</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13:44:00</t>
+          <t>13:43:58</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:45:01</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>13:46:00</t>
+          <t>13:45:59</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>13:47:00</t>
+          <t>13:47:04</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>13:48:00</t>
+          <t>13:48:02</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>13:49:00</t>
+          <t>13:49:01</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>13:50:03</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>13:51:00</t>
+          <t>13:51:01</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>13:52:00</t>
+          <t>13:52:01</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>13:53:00</t>
+          <t>13:53:01</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>13:54:00</t>
+          <t>13:53:59</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>13:57:00</t>
+          <t>13:56:59</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>13:59:00</t>
+          <t>13:59:01</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>14:00:01</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>14:01:00</t>
+          <t>14:01:03</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>14:02:00</t>
+          <t>14:02:01</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>14:03:00</t>
+          <t>14:02:59</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>14:05:00</t>
+          <t>14:04:59</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>14:06:00</t>
+          <t>14:06:01</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>14:08:00</t>
+          <t>14:07:59</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>14:09:00</t>
+          <t>14:08:59</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>14:14:00</t>
+          <t>14:13:59</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>14:15:00</t>
+          <t>14:14:58</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>14:16:00</t>
+          <t>14:15:58</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>14:18:00</t>
+          <t>14:17:59</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>14:19:00</t>
+          <t>14:19:01</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>14:20:00</t>
+          <t>14:20:01</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>14:22:00</t>
+          <t>14:22:02</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>14:23:00</t>
+          <t>14:23:03</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>14:24:00</t>
+          <t>14:23:58</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>14:25:00</t>
+          <t>14:25:01</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>14:27:00</t>
+          <t>14:26:58</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>14:28:00</t>
+          <t>14:27:58</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>14:29:00</t>
+          <t>14:29:01</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:29:59</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>14:32:00</t>
+          <t>14:32:01</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>14:33:00</t>
+          <t>14:32:59</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>14:35:00</t>
+          <t>14:35:01</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>14:36:00</t>
+          <t>14:36:01</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>14:37:00</t>
+          <t>14:36:58</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>14:38:00</t>
+          <t>14:37:58</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>14:39:00</t>
+          <t>14:39:02</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>14:40:00</t>
+          <t>14:40:02</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>14:41:00</t>
+          <t>14:40:59</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>14:42:00</t>
+          <t>14:41:58</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>14:44:00</t>
+          <t>14:43:58</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:45:01</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>14:46:00</t>
+          <t>14:45:59</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>14:58:00</t>
+          <t>14:57:59</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>AIN</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>14:59:00</t>
+          <t>14:58:59</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>15:01:00</t>
+          <t>15:00:59</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>15:02:00</t>
+          <t>15:02:01</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>15:03:00</t>
+          <t>15:02:58</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>15:04:00</t>
+          <t>15:03:58</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>15:05:00</t>
+          <t>15:04:58</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>15:06:00</t>
+          <t>15:05:58</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>15:09:00</t>
+          <t>15:08:59</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>15:10:00</t>
+          <t>15:09:59</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>15:11:00</t>
+          <t>15:10:58</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>15:14:00</t>
+          <t>15:13:59</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>15:16:00</t>
+          <t>15:15:59</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>15:17:00</t>
+          <t>15:17:01</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>15:18:00</t>
+          <t>15:17:59</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>15:19:00</t>
+          <t>15:18:59</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>15:20:00</t>
+          <t>15:20:01</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>15:21:00</t>
+          <t>15:20:58</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>15:24:00</t>
+          <t>15:23:58</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>15:29:00</t>
+          <t>15:28:59</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:30:02</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>15:31:00</t>
+          <t>15:30:58</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>15:32:00</t>
+          <t>15:32:01</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>15:33:00</t>
+          <t>15:32:59</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>15:34:00</t>
+          <t>15:33:58</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>15:35:00</t>
+          <t>15:34:59</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>15:37:00</t>
+          <t>15:36:58</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>15:38:00</t>
+          <t>15:37:59</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>15:39:00</t>
+          <t>15:39:01</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>15:40:00</t>
+          <t>15:40:01</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>15:42:00</t>
+          <t>15:41:59</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>15:43:00</t>
+          <t>15:42:59</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>15:44:00</t>
+          <t>15:43:58</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>15:46:00</t>
+          <t>15:46:01</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>15:47:00</t>
+          <t>15:46:58</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>15:48:00</t>
+          <t>15:47:58</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>15:49:00</t>
+          <t>15:49:01</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>15:53:00</t>
+          <t>15:52:59</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>09:45:00</t>
+          <t>09:45:03</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>09:46:30</t>
+          <t>09:46:31</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>09:48:00</t>
+          <t>09:48:01</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>09:49:30</t>
+          <t>09:49:31</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>10:04:30</t>
+          <t>10:04:36</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>10:06:00</t>
+          <t>10:06:05</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>10:07:30</t>
+          <t>10:07:33</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>10:10:30</t>
+          <t>10:10:34</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>10:12:00</t>
+          <t>10:12:02</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>10:15:00</t>
+          <t>10:15:07</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>10:16:30</t>
+          <t>10:16:33</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>10:19:30</t>
+          <t>10:19:31</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>10:21:00</t>
+          <t>10:21:03</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>10:22:30</t>
+          <t>10:22:34</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>10:25:30</t>
+          <t>10:25:35</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>10:27:00</t>
+          <t>10:27:02</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>10:28:30</t>
+          <t>10:28:31</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>10:30:00</t>
+          <t>10:30:02</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>10:31:30</t>
+          <t>10:31:26</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>10:33:00</t>
+          <t>10:33:03</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>10:39:30</t>
+          <t>10:39:29</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>10:41:00</t>
+          <t>10:41:04</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>10:44:00</t>
+          <t>10:44:01</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>10:45:30</t>
+          <t>10:45:32</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>10:47:00</t>
+          <t>10:47:01</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>10:48:30</t>
+          <t>10:48:33</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>10:50:00</t>
+          <t>10:50:03</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>10:53:00</t>
+          <t>10:53:02</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>10:54:30</t>
+          <t>10:54:25</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>10:56:00</t>
+          <t>10:56:01</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>10:57:30</t>
+          <t>10:57:31</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>10:59:00</t>
+          <t>10:59:01</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -11484,7 +11484,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>11:00:30</t>
+          <t>11:00:28</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>11:02:00</t>
+          <t>11:02:01</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>11:06:30</t>
+          <t>11:06:33</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>11:08:00</t>
+          <t>11:08:02</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>11:13:00</t>
+          <t>11:12:59</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>11:16:00</t>
+          <t>11:16:02</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>11:17:30</t>
+          <t>11:17:28</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>11:20:30</t>
+          <t>11:20:31</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>11:23:30</t>
+          <t>11:23:31</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>11:25:00</t>
+          <t>11:24:58</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>11:26:30</t>
+          <t>11:26:31</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>11:28:00</t>
+          <t>11:27:59</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>11:29:30</t>
+          <t>11:29:28</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -12600,7 +12600,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>11:31:00</t>
+          <t>11:31:01</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -12662,7 +12662,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>11:32:30</t>
+          <t>11:32:29</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>11:35:30</t>
+          <t>11:35:31</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>11:37:00</t>
+          <t>11:37:01</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>11:38:30</t>
+          <t>11:38:31</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>11:40:00</t>
+          <t>11:40:03</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>11:51:00</t>
+          <t>11:51:02</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>11:52:30</t>
+          <t>11:52:34</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -13220,12 +13220,12 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>11:54:00</t>
+          <t>11:54:03</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>AIN</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J198" t="n">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>11:55:30</t>
+          <t>11:55:34</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>11:57:00</t>
+          <t>11:56:59</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:59:59</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>12:01:30</t>
+          <t>12:01:32</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>12:03:00</t>
+          <t>12:03:04</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>12:04:30</t>
+          <t>12:04:32</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>12:06:00</t>
+          <t>12:05:59</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>12:07:30</t>
+          <t>12:07:29</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>12:09:00</t>
+          <t>12:09:03</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>12:10:30</t>
+          <t>12:10:32</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>12:12:00</t>
+          <t>12:12:04</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>12:13:30</t>
+          <t>12:13:29</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>12:15:00</t>
+          <t>12:15:01</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>12:16:30</t>
+          <t>12:16:35</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>12:18:00</t>
+          <t>12:18:01</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>12:19:30</t>
+          <t>12:19:33</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>12:22:30</t>
+          <t>12:22:33</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>12:24:00</t>
+          <t>12:24:01</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>12:27:00</t>
+          <t>12:27:01</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>12:32:00</t>
+          <t>12:32:03</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>12:33:30</t>
+          <t>12:33:33</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>12:35:00</t>
+          <t>12:35:01</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14832,7 +14832,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>12:36:30</t>
+          <t>12:36:33</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14956,7 +14956,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>12:39:30</t>
+          <t>12:39:34</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>12:41:00</t>
+          <t>12:41:01</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>12:42:30</t>
+          <t>12:42:33</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>12:44:00</t>
+          <t>12:44:04</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>12:47:00</t>
+          <t>12:47:03</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>12:48:30</t>
+          <t>12:48:32</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>12:50:00</t>
+          <t>12:50:01</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -15452,7 +15452,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>12:51:30</t>
+          <t>12:51:31</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>12:53:00</t>
+          <t>12:53:03</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>12:54:30</t>
+          <t>12:54:33</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>12:56:00</t>
+          <t>12:56:01</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>12:59:00</t>
+          <t>12:59:01</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -16010,7 +16010,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>13:05:00</t>
+          <t>13:05:04</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>13:06:30</t>
+          <t>13:06:33</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>13:08:00</t>
+          <t>13:08:03</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:30:02</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>14:32:30</t>
+          <t>14:32:27</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>14:38:00</t>
+          <t>14:37:59</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>14:40:30</t>
+          <t>14:40:32</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>14:43:00</t>
+          <t>14:43:01</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -16558,7 +16558,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>14:45:30</t>
+          <t>14:45:29</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>14:48:00</t>
+          <t>14:47:58</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>14:50:30</t>
+          <t>14:50:29</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -16780,7 +16780,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>14:53:00</t>
+          <t>14:52:59</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>14:59:00</t>
+          <t>14:58:59</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>15:01:30</t>
+          <t>15:01:29</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -17076,7 +17076,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>15:06:30</t>
+          <t>15:06:26</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>15:09:00</t>
+          <t>15:08:57</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>15:11:30</t>
+          <t>15:11:29</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>15:27:00</t>
+          <t>15:27:01</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -17520,7 +17520,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>15:29:30</t>
+          <t>15:29:29</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -17668,7 +17668,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>15:38:00</t>
+          <t>15:38:02</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -17742,7 +17742,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>15:40:30</t>
+          <t>15:40:31</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>15:43:00</t>
+          <t>15:43:02</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -17890,7 +17890,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>15:45:30</t>
+          <t>15:45:32</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -17964,7 +17964,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>08:50:00</t>
+          <t>08:49:59</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>08:51:30</t>
+          <t>08:51:28</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -18088,7 +18088,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>08:53:00</t>
+          <t>08:52:59</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -18150,7 +18150,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>08:54:30</t>
+          <t>08:54:28</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>09:03:00</t>
+          <t>09:03:09</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -18274,7 +18274,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>09:06:00</t>
+          <t>09:06:06</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -18336,12 +18336,12 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>09:07:30</t>
+          <t>09:07:33</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>AIN</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J276" t="n">
@@ -18460,7 +18460,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>09:10:30</t>
+          <t>09:10:33</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -18584,7 +18584,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>09:13:30</t>
+          <t>09:13:36</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>09:15:00</t>
+          <t>09:15:01</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -18708,7 +18708,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>09:16:30</t>
+          <t>09:16:29</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -18770,7 +18770,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>09:18:00</t>
+          <t>09:17:59</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>09:19:30</t>
+          <t>09:19:29</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -18894,7 +18894,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>09:21:00</t>
+          <t>09:21:02</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -19018,7 +19018,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>09:24:00</t>
+          <t>09:24:03</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>09:25:30</t>
+          <t>09:25:31</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -19142,7 +19142,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>09:27:00</t>
+          <t>09:26:58</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>09:28:30</t>
+          <t>09:28:34</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -19266,7 +19266,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>09:30:03</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -19328,7 +19328,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>09:35:00</t>
+          <t>09:35:03</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -19390,7 +19390,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>09:36:30</t>
+          <t>09:36:33</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -19452,7 +19452,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>09:38:00</t>
+          <t>09:38:03</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>09:39:30</t>
+          <t>09:39:31</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>09:41:00</t>
+          <t>09:41:05</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -19638,7 +19638,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>09:42:30</t>
+          <t>09:42:34</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -19700,7 +19700,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>09:44:00</t>
+          <t>09:44:03</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -19762,7 +19762,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>09:45:30</t>
+          <t>09:45:33</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>09:47:00</t>
+          <t>09:47:01</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -19948,7 +19948,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>09:50:00</t>
+          <t>09:50:02</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -20010,7 +20010,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>09:51:30</t>
+          <t>09:51:33</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -20072,7 +20072,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>09:53:00</t>
+          <t>09:53:03</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>09:54:30</t>
+          <t>09:54:31</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>09:56:00</t>
+          <t>09:55:58</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>09:57:30</t>
+          <t>09:57:31</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -20320,7 +20320,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>09:59:00</t>
+          <t>09:59:01</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -20382,7 +20382,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>10:00:30</t>
+          <t>10:00:31</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -20444,7 +20444,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>10:05:30</t>
+          <t>10:05:29</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>10:07:00</t>
+          <t>10:07:02</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -20568,7 +20568,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>10:08:30</t>
+          <t>10:08:31</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -20630,7 +20630,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>10:10:00</t>
+          <t>10:10:01</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>10:11:30</t>
+          <t>10:11:29</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -20754,7 +20754,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>10:13:00</t>
+          <t>10:13:03</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>10:14:30</t>
+          <t>10:14:31</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -20878,7 +20878,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>10:16:00</t>
+          <t>10:16:05</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -20940,7 +20940,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>10:17:30</t>
+          <t>10:17:32</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -21002,7 +21002,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>10:19:00</t>
+          <t>10:19:03</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -21064,7 +21064,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>10:20:30</t>
+          <t>10:20:32</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -21126,7 +21126,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>10:22:00</t>
+          <t>10:22:02</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -21188,7 +21188,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>10:23:30</t>
+          <t>10:23:36</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -21250,7 +21250,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>10:25:00</t>
+          <t>10:25:02</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>10:26:30</t>
+          <t>10:26:31</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>10:28:00</t>
+          <t>10:28:02</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -21436,7 +21436,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>10:29:30</t>
+          <t>10:29:31</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -21498,7 +21498,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>10:31:00</t>
+          <t>10:31:02</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -21684,7 +21684,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>10:43:00</t>
+          <t>10:43:03</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>10:46:00</t>
+          <t>10:46:03</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -21870,7 +21870,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>10:47:30</t>
+          <t>10:47:34</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>10:49:00</t>
+          <t>10:49:01</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>10:50:30</t>
+          <t>10:50:31</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -22056,7 +22056,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>10:52:00</t>
+          <t>10:52:03</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -22118,7 +22118,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>10:53:30</t>
+          <t>10:53:31</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -22180,7 +22180,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>10:55:00</t>
+          <t>10:55:01</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -22242,7 +22242,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>10:56:30</t>
+          <t>10:56:35</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -22304,7 +22304,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>10:58:00</t>
+          <t>10:58:04</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -22366,7 +22366,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>10:59:30</t>
+          <t>10:59:32</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -22428,7 +22428,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>11:01:00</t>
+          <t>11:01:04</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -22490,7 +22490,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>11:02:30</t>
+          <t>11:02:29</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -22552,7 +22552,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>11:04:00</t>
+          <t>11:04:02</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -22676,7 +22676,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>11:07:00</t>
+          <t>11:07:05</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -22738,7 +22738,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>11:12:00</t>
+          <t>11:12:01</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -22800,7 +22800,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>11:13:30</t>
+          <t>11:13:31</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -22986,7 +22986,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>11:18:00</t>
+          <t>11:17:56</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -23048,7 +23048,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>11:19:30</t>
+          <t>11:19:29</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -23110,7 +23110,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>11:21:00</t>
+          <t>11:21:01</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -23172,7 +23172,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>11:22:30</t>
+          <t>11:22:29</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -23296,7 +23296,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>11:25:30</t>
+          <t>11:25:33</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -23358,7 +23358,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>11:27:00</t>
+          <t>11:27:01</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -23420,7 +23420,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>11:28:30</t>
+          <t>11:28:29</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -23482,7 +23482,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>11:30:02</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>11:34:30</t>
+          <t>11:34:28</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -23730,7 +23730,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>11:36:00</t>
+          <t>11:36:02</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -23792,7 +23792,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>11:37:30</t>
+          <t>11:37:29</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -23854,7 +23854,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>11:39:00</t>
+          <t>11:39:01</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>11:44:00</t>
+          <t>11:44:06</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -23978,7 +23978,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>11:45:30</t>
+          <t>11:45:31</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -24102,7 +24102,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>11:48:30</t>
+          <t>11:48:31</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>11:50:00</t>
+          <t>11:50:02</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -24226,7 +24226,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>11:51:30</t>
+          <t>11:51:31</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -24288,7 +24288,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>11:53:00</t>
+          <t>11:53:03</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>11:54:30</t>
+          <t>11:54:31</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -24412,7 +24412,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>11:56:00</t>
+          <t>11:56:02</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -24474,7 +24474,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>11:57:30</t>
+          <t>11:57:28</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -24536,7 +24536,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>11:59:00</t>
+          <t>11:58:59</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -24598,7 +24598,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>12:00:30</t>
+          <t>12:00:31</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -24660,7 +24660,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>12:02:00</t>
+          <t>12:02:02</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -24722,7 +24722,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>12:03:30</t>
+          <t>12:03:31</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -24784,7 +24784,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>12:05:00</t>
+          <t>12:05:03</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -24908,7 +24908,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>12:08:00</t>
+          <t>12:08:02</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -25032,7 +25032,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>12:11:00</t>
+          <t>12:11:01</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -25094,7 +25094,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>12:16:00</t>
+          <t>12:15:58</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -25218,7 +25218,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>12:19:00</t>
+          <t>12:19:02</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -25280,7 +25280,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>12:20:30</t>
+          <t>12:20:31</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -25342,7 +25342,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>12:22:00</t>
+          <t>12:22:01</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -25404,7 +25404,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>12:23:30</t>
+          <t>12:23:32</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -25466,7 +25466,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>12:25:00</t>
+          <t>12:25:01</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -25528,7 +25528,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>12:26:30</t>
+          <t>12:26:33</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -25652,7 +25652,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>12:29:30</t>
+          <t>12:29:31</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -25714,7 +25714,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>12:31:00</t>
+          <t>12:30:59</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -25776,7 +25776,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>12:32:30</t>
+          <t>12:32:29</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -25838,7 +25838,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>12:34:00</t>
+          <t>12:34:03</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -25962,7 +25962,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>12:37:00</t>
+          <t>12:36:59</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -26024,7 +26024,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>12:38:30</t>
+          <t>12:38:27</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -26086,7 +26086,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>12:40:00</t>
+          <t>12:39:58</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -26148,7 +26148,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>12:41:30</t>
+          <t>12:41:27</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -26210,7 +26210,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>14:10:00</t>
+          <t>14:10:02</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -26350,7 +26350,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>14:20:00</t>
+          <t>14:19:57</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -26424,7 +26424,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>14:22:30</t>
+          <t>14:22:26</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -26572,7 +26572,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>14:27:30</t>
+          <t>14:27:31</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -26794,7 +26794,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>14:35:00</t>
+          <t>14:35:03</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -26868,7 +26868,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>14:37:30</t>
+          <t>14:37:33</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>14:40:00</t>
+          <t>14:40:01</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -27016,7 +27016,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>14:42:30</t>
+          <t>14:42:32</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -27090,7 +27090,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:45:01</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -27164,7 +27164,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>14:47:30</t>
+          <t>14:47:31</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -27312,7 +27312,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:00:01</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -27386,7 +27386,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>15:02:30</t>
+          <t>15:02:29</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -27460,7 +27460,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>15:05:00</t>
+          <t>15:04:57</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -27682,7 +27682,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>15:12:30</t>
+          <t>15:12:28</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -27756,7 +27756,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>15:14:59</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -27830,7 +27830,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>15:17:30</t>
+          <t>15:17:32</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -27904,7 +27904,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>15:20:00</t>
+          <t>15:19:58</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -27978,7 +27978,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>15:22:30</t>
+          <t>15:22:34</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -28052,7 +28052,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>15:28:30</t>
+          <t>15:28:31</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -28126,7 +28126,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>15:31:00</t>
+          <t>15:31:01</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -28200,7 +28200,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>15:33:30</t>
+          <t>15:33:31</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -28274,7 +28274,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>15:36:00</t>
+          <t>15:35:58</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -28348,7 +28348,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>15:38:30</t>
+          <t>15:38:29</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -28422,7 +28422,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>15:41:00</t>
+          <t>15:40:56</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -28496,7 +28496,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>15:43:30</t>
+          <t>15:43:29</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -28570,7 +28570,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>15:46:00</t>
+          <t>15:45:55</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>15:48:30</t>
+          <t>15:48:29</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -28718,7 +28718,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>10:15:00</t>
+          <t>10:15:03</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -28780,7 +28780,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>10:17:00</t>
+          <t>10:17:01</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -28842,7 +28842,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>10:19:00</t>
+          <t>10:19:02</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -28904,7 +28904,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>10:21:00</t>
+          <t>10:21:01</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -29090,7 +29090,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>10:37:00</t>
+          <t>10:37:02</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -29214,7 +29214,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>10:41:00</t>
+          <t>10:41:04</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -29276,7 +29276,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>10:43:00</t>
+          <t>10:43:03</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -29338,7 +29338,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>10:45:00</t>
+          <t>10:44:59</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>10:47:00</t>
+          <t>10:46:57</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>10:51:00</t>
+          <t>10:50:58</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -29586,7 +29586,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>10:53:00</t>
+          <t>10:52:55</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -29648,7 +29648,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>10:55:00</t>
+          <t>10:54:59</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>10:59:00</t>
+          <t>10:59:02</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>11:01:00</t>
+          <t>11:00:56</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -29896,7 +29896,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>11:03:00</t>
+          <t>11:02:59</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -29958,7 +29958,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>11:05:00</t>
+          <t>11:04:57</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>11:07:00</t>
+          <t>11:07:05</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -30082,7 +30082,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>11:09:00</t>
+          <t>11:09:03</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -30144,7 +30144,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>11:11:00</t>
+          <t>11:10:59</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -30206,7 +30206,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>11:13:00</t>
+          <t>11:13:01</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -30268,7 +30268,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>11:15:00</t>
+          <t>11:14:58</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -30330,7 +30330,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>11:17:00</t>
+          <t>11:17:03</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -30392,7 +30392,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>11:19:00</t>
+          <t>11:19:01</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -30516,7 +30516,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>11:23:00</t>
+          <t>11:23:02</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -30578,7 +30578,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>11:25:00</t>
+          <t>11:25:01</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -30640,7 +30640,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>11:27:00</t>
+          <t>11:27:02</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -30702,7 +30702,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>11:29:00</t>
+          <t>11:28:59</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -30764,7 +30764,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>11:31:00</t>
+          <t>11:31:02</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -30826,7 +30826,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>11:38:00</t>
+          <t>11:37:58</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -30888,7 +30888,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>11:40:00</t>
+          <t>11:40:01</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -30950,12 +30950,12 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>11:42:00</t>
+          <t>11:42:01</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>AIN</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J473" t="n">
@@ -31012,7 +31012,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>11:44:00</t>
+          <t>11:44:01</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>11:46:00</t>
+          <t>11:45:59</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -31136,7 +31136,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>11:48:00</t>
+          <t>11:48:01</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -31198,7 +31198,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>11:50:00</t>
+          <t>11:49:59</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -31260,7 +31260,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>11:52:00</t>
+          <t>11:52:03</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -31322,7 +31322,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>11:54:00</t>
+          <t>11:54:03</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -31384,7 +31384,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>11:56:00</t>
+          <t>11:56:01</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -31446,7 +31446,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>11:58:00</t>
+          <t>11:57:59</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -31508,7 +31508,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>12:00:01</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -31632,7 +31632,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>12:04:00</t>
+          <t>12:04:01</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -31694,7 +31694,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>12:06:00</t>
+          <t>12:05:59</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -31818,7 +31818,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>12:10:00</t>
+          <t>12:10:02</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -31880,7 +31880,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>12:12:00</t>
+          <t>12:12:07</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -31942,7 +31942,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>12:14:00</t>
+          <t>12:14:01</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>12:16:00</t>
+          <t>12:16:06</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -32066,7 +32066,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>12:18:00</t>
+          <t>12:18:02</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -32128,7 +32128,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>12:20:03</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -32190,7 +32190,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>12:22:00</t>
+          <t>12:22:01</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -32314,7 +32314,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>12:26:00</t>
+          <t>12:26:02</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -32562,7 +32562,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>12:34:00</t>
+          <t>12:34:01</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -32624,7 +32624,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>12:36:00</t>
+          <t>12:36:01</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -32752,7 +32752,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>13:05:00</t>
+          <t>13:05:01</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>13:07:00</t>
+          <t>13:06:59</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -32884,7 +32884,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>13:09:00</t>
+          <t>13:09:01</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -32950,7 +32950,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>13:11:00</t>
+          <t>13:11:02</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -33016,7 +33016,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>13:13:00</t>
+          <t>13:12:58</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -33148,7 +33148,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>13:20:30</t>
+          <t>13:20:31</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -33214,7 +33214,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>13:22:30</t>
+          <t>13:22:29</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -33280,7 +33280,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>13:24:30</t>
+          <t>13:24:31</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -33478,7 +33478,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>13:36:00</t>
+          <t>13:36:02</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>13:38:00</t>
+          <t>13:38:01</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -33610,7 +33610,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>13:40:00</t>
+          <t>13:39:58</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -33676,7 +33676,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>13:42:00</t>
+          <t>13:42:04</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -33742,7 +33742,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>13:44:00</t>
+          <t>13:44:01</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -33808,7 +33808,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>13:46:00</t>
+          <t>13:45:59</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -33940,7 +33940,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>13:53:30</t>
+          <t>13:53:32</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -34006,7 +34006,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>13:55:30</t>
+          <t>13:55:31</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -34072,7 +34072,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>13:57:30</t>
+          <t>13:57:33</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -34138,7 +34138,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>13:59:30</t>
+          <t>13:59:34</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -34204,7 +34204,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>14:01:30</t>
+          <t>14:01:32</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -34270,7 +34270,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>10:15:00</t>
+          <t>10:14:59</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -34332,7 +34332,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>10:17:00</t>
+          <t>10:17:01</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -34394,7 +34394,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>10:19:00</t>
+          <t>10:18:59</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>10:21:00</t>
+          <t>10:20:59</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -34580,7 +34580,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>10:35:00</t>
+          <t>10:35:02</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -34642,7 +34642,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>10:37:00</t>
+          <t>10:37:04</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -34704,7 +34704,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>10:39:00</t>
+          <t>10:39:03</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -34890,7 +34890,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>10:45:00</t>
+          <t>10:45:01</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -34952,7 +34952,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>10:47:00</t>
+          <t>10:47:01</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>10:49:00</t>
+          <t>10:49:01</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -35076,7 +35076,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>10:51:00</t>
+          <t>10:51:01</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -35138,7 +35138,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>10:53:00</t>
+          <t>10:53:03</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -35200,7 +35200,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>10:55:00</t>
+          <t>10:55:01</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -35262,7 +35262,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>10:57:00</t>
+          <t>10:56:58</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -35386,7 +35386,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>11:01:00</t>
+          <t>11:01:04</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -35448,7 +35448,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>11:03:00</t>
+          <t>11:02:59</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -35572,7 +35572,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>11:07:00</t>
+          <t>11:07:02</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -35634,7 +35634,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>11:09:00</t>
+          <t>11:09:01</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -35696,7 +35696,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>11:11:00</t>
+          <t>11:11:03</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -35758,7 +35758,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>11:13:00</t>
+          <t>11:13:01</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -35820,7 +35820,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>11:15:00</t>
+          <t>11:15:03</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -35882,7 +35882,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>11:17:00</t>
+          <t>11:16:59</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -35944,7 +35944,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>11:19:00</t>
+          <t>11:19:04</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -36068,7 +36068,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>11:23:00</t>
+          <t>11:23:03</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -36130,7 +36130,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>11:25:00</t>
+          <t>11:25:01</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -36254,7 +36254,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>11:29:00</t>
+          <t>11:29:02</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -36316,7 +36316,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>11:31:00</t>
+          <t>11:31:02</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -36378,7 +36378,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>11:38:00</t>
+          <t>11:38:01</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -36502,7 +36502,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>11:42:00</t>
+          <t>11:42:02</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -36564,7 +36564,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>11:44:00</t>
+          <t>11:44:02</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -36688,7 +36688,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>11:48:00</t>
+          <t>11:48:01</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -36812,7 +36812,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>11:52:00</t>
+          <t>11:52:01</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -36874,7 +36874,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>11:54:00</t>
+          <t>11:53:59</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -36936,7 +36936,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>11:56:00</t>
+          <t>11:55:58</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -36998,7 +36998,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>11:58:00</t>
+          <t>11:57:59</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -37060,7 +37060,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>12:00:01</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -37122,7 +37122,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>12:02:00</t>
+          <t>12:02:02</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -37184,7 +37184,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>12:04:00</t>
+          <t>12:04:07</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -37246,7 +37246,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>12:06:00</t>
+          <t>12:05:59</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -37308,7 +37308,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>12:08:00</t>
+          <t>12:08:05</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -37370,7 +37370,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>12:10:00</t>
+          <t>12:10:02</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -37494,7 +37494,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>12:14:00</t>
+          <t>12:13:57</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -37556,7 +37556,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>12:16:00</t>
+          <t>12:16:01</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -37680,7 +37680,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>12:19:59</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -37742,7 +37742,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>12:22:00</t>
+          <t>12:22:01</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -37804,7 +37804,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>12:24:00</t>
+          <t>12:24:01</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -37866,7 +37866,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>12:26:00</t>
+          <t>12:25:59</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -37928,7 +37928,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>12:28:00</t>
+          <t>12:27:59</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -37990,7 +37990,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:30:02</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -38052,7 +38052,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>12:32:00</t>
+          <t>12:31:58</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -38114,7 +38114,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>12:34:00</t>
+          <t>12:34:01</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -38176,7 +38176,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>12:36:00</t>
+          <t>12:36:01</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -38304,7 +38304,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>14:35:30</t>
+          <t>14:35:33</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -38370,7 +38370,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>14:38:00</t>
+          <t>14:38:01</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -38436,7 +38436,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>14:40:30</t>
+          <t>14:40:33</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -38568,7 +38568,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>14:49:00</t>
+          <t>14:49:01</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -38634,7 +38634,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>14:51:30</t>
+          <t>14:51:32</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -38700,7 +38700,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>14:54:00</t>
+          <t>14:53:58</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -38766,7 +38766,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:00:01</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -38832,7 +38832,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>15:02:30</t>
+          <t>15:02:31</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -38898,7 +38898,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>15:05:00</t>
+          <t>15:05:04</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -38964,7 +38964,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>15:07:30</t>
+          <t>15:07:31</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -39030,7 +39030,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>15:17:00</t>
+          <t>15:17:02</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -39162,7 +39162,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>15:22:00</t>
+          <t>15:21:59</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -39228,7 +39228,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>15:24:30</t>
+          <t>15:24:28</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -39294,7 +39294,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>15:30:30</t>
+          <t>15:30:27</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -39426,7 +39426,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>15:35:30</t>
+          <t>15:35:31</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -39492,7 +39492,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>15:38:00</t>
+          <t>15:37:59</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>15:44:00</t>
+          <t>15:43:58</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -39690,7 +39690,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>15:49:00</t>
+          <t>15:49:03</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -39756,7 +39756,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>15:51:30</t>
+          <t>15:51:26</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -39824,7 +39824,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>10:03:00</t>
+          <t>10:03:05</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -39892,7 +39892,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>10:03:00</t>
+          <t>10:03:05</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -39960,7 +39960,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>10:03:00</t>
+          <t>10:03:05</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -40028,12 +40028,12 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>10:06:00</t>
+          <t>10:06:03</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>AIN</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J616" t="n">
@@ -40096,7 +40096,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>10:06:00</t>
+          <t>10:06:03</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -40164,7 +40164,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>10:06:00</t>
+          <t>10:06:03</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -40232,7 +40232,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>10:09:00</t>
+          <t>10:09:20</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -40300,7 +40300,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>10:09:00</t>
+          <t>10:09:20</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -40368,7 +40368,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>10:09:00</t>
+          <t>10:09:20</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -40436,7 +40436,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>10:09:00</t>
+          <t>10:09:20</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -40776,7 +40776,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>10:15:00</t>
+          <t>10:17:15</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -40844,7 +40844,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>10:15:00</t>
+          <t>10:17:15</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -40912,7 +40912,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>10:15:00</t>
+          <t>10:17:15</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -40980,7 +40980,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>10:15:00</t>
+          <t>10:17:15</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -41048,7 +41048,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>10:18:00</t>
+          <t>10:19:34</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -41116,7 +41116,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>10:18:00</t>
+          <t>10:19:34</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -41184,7 +41184,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>10:18:00</t>
+          <t>10:19:34</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -41252,7 +41252,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>10:18:00</t>
+          <t>10:19:34</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -41320,7 +41320,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>10:21:00</t>
+          <t>10:22:38</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -41388,7 +41388,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>10:21:00</t>
+          <t>10:22:38</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -41456,7 +41456,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>10:21:00</t>
+          <t>10:22:38</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -41524,7 +41524,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>10:21:00</t>
+          <t>10:22:38</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -41592,7 +41592,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>10:24:00</t>
+          <t>10:26:00</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -41660,7 +41660,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>10:24:00</t>
+          <t>10:26:00</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -41728,7 +41728,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>10:24:00</t>
+          <t>10:26:00</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -41796,7 +41796,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>10:24:00</t>
+          <t>10:26:00</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -41864,7 +41864,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>10:27:00</t>
+          <t>10:28:59</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -41932,7 +41932,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>10:27:00</t>
+          <t>10:28:59</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -42000,7 +42000,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>10:27:00</t>
+          <t>10:28:59</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -42068,7 +42068,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>10:27:00</t>
+          <t>10:28:59</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -42136,7 +42136,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>10:30:00</t>
+          <t>10:31:11</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>10:30:00</t>
+          <t>10:31:11</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -42272,7 +42272,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>10:30:00</t>
+          <t>10:31:11</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -42340,7 +42340,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>10:30:00</t>
+          <t>10:31:11</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -42408,7 +42408,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>10:33:00</t>
+          <t>10:33:27</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -42476,7 +42476,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>10:33:00</t>
+          <t>10:33:27</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -42544,7 +42544,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>10:33:00</t>
+          <t>10:33:27</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -42612,7 +42612,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>10:33:00</t>
+          <t>10:33:27</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -42680,7 +42680,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>10:41:00</t>
+          <t>10:40:59</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -42748,7 +42748,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>10:41:00</t>
+          <t>10:40:59</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -42816,7 +42816,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>10:41:00</t>
+          <t>10:40:59</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -42884,7 +42884,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>10:44:00</t>
+          <t>10:44:14</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -42952,7 +42952,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>10:44:00</t>
+          <t>10:44:14</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -43020,7 +43020,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>10:44:00</t>
+          <t>10:44:14</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -43088,7 +43088,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>10:47:00</t>
+          <t>10:46:57</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -43156,7 +43156,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>10:47:00</t>
+          <t>10:46:57</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -43224,7 +43224,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>10:47:00</t>
+          <t>10:46:57</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -43292,7 +43292,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>10:47:00</t>
+          <t>10:46:57</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -43360,7 +43360,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>10:50:00</t>
+          <t>10:50:52</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -43428,7 +43428,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>10:50:00</t>
+          <t>10:50:52</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -43496,7 +43496,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>10:50:00</t>
+          <t>10:50:52</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -43564,7 +43564,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>10:50:00</t>
+          <t>10:50:52</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -43632,7 +43632,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>10:53:00</t>
+          <t>10:54:45</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -43700,7 +43700,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>10:53:00</t>
+          <t>10:54:45</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -43768,7 +43768,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>10:53:00</t>
+          <t>10:54:45</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -43836,7 +43836,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>10:53:00</t>
+          <t>10:54:45</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -43904,7 +43904,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>10:56:00</t>
+          <t>10:57:20</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -43972,7 +43972,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>10:56:00</t>
+          <t>10:57:20</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -44040,7 +44040,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>10:56:00</t>
+          <t>10:57:20</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -44108,7 +44108,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>10:56:00</t>
+          <t>10:57:20</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -44176,7 +44176,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>10:59:00</t>
+          <t>11:00:37</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -44244,7 +44244,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>10:59:00</t>
+          <t>11:00:37</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -44312,7 +44312,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>10:59:00</t>
+          <t>11:00:37</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -44380,7 +44380,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>10:59:00</t>
+          <t>11:00:37</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -44448,7 +44448,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>11:02:00</t>
+          <t>11:02:55</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -44516,7 +44516,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>11:02:00</t>
+          <t>11:02:55</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -44584,7 +44584,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>11:02:00</t>
+          <t>11:02:55</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -44652,7 +44652,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>11:02:00</t>
+          <t>11:02:55</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -44720,7 +44720,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>11:05:00</t>
+          <t>11:05:45</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -44788,7 +44788,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>11:05:00</t>
+          <t>11:05:45</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -44856,7 +44856,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>11:05:00</t>
+          <t>11:05:45</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -44924,7 +44924,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>11:05:00</t>
+          <t>11:05:45</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -44992,7 +44992,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>11:08:00</t>
+          <t>11:10:03</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -45060,7 +45060,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>11:08:00</t>
+          <t>11:10:03</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -45128,7 +45128,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>11:08:00</t>
+          <t>11:10:03</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -45196,7 +45196,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>11:08:00</t>
+          <t>11:10:03</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -45264,7 +45264,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>11:11:00</t>
+          <t>11:14:39</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -45332,7 +45332,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>11:11:00</t>
+          <t>11:14:39</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -45400,7 +45400,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>11:11:00</t>
+          <t>11:14:39</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -45468,7 +45468,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>11:11:00</t>
+          <t>11:14:39</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -45808,7 +45808,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>11:25:00</t>
+          <t>11:24:35</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -45876,7 +45876,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>11:25:00</t>
+          <t>11:24:35</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>11:25:00</t>
+          <t>11:24:35</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -46012,7 +46012,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>11:25:00</t>
+          <t>11:24:35</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -46080,7 +46080,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>11:28:00</t>
+          <t>11:27:38</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -46148,7 +46148,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>11:28:00</t>
+          <t>11:27:38</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -46216,7 +46216,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>11:28:00</t>
+          <t>11:27:38</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -46284,7 +46284,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>11:28:00</t>
+          <t>11:27:38</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -46352,7 +46352,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>11:31:00</t>
+          <t>11:30:59</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -46420,7 +46420,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>11:31:00</t>
+          <t>11:30:59</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -46488,7 +46488,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>11:31:00</t>
+          <t>11:30:59</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -46556,7 +46556,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>11:31:00</t>
+          <t>11:30:59</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -46624,12 +46624,12 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>11:34:00</t>
+          <t>11:34:01</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>AIN</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="J713" t="n">
@@ -46692,7 +46692,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>11:34:00</t>
+          <t>11:34:01</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -46760,7 +46760,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>11:34:00</t>
+          <t>11:34:01</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -46828,7 +46828,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>11:34:00</t>
+          <t>11:34:01</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -46896,7 +46896,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>11:42:00</t>
+          <t>11:42:01</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -46964,7 +46964,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>11:42:00</t>
+          <t>11:42:01</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -47032,7 +47032,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>11:42:00</t>
+          <t>11:42:01</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -47100,7 +47100,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>11:42:00</t>
+          <t>11:42:01</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -47168,7 +47168,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>11:45:00</t>
+          <t>11:44:59</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -47236,7 +47236,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>11:45:00</t>
+          <t>11:44:59</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -47304,7 +47304,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>11:45:00</t>
+          <t>11:44:59</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -47372,7 +47372,7 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>11:45:00</t>
+          <t>11:44:59</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -47440,7 +47440,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>11:48:00</t>
+          <t>11:50:25</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -47508,7 +47508,7 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>11:48:00</t>
+          <t>11:50:25</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -47576,7 +47576,7 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>11:48:00</t>
+          <t>11:50:25</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -47644,7 +47644,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>11:48:00</t>
+          <t>11:50:25</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -47712,7 +47712,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>11:51:00</t>
+          <t>11:53:17</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -47780,7 +47780,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>11:51:00</t>
+          <t>11:53:17</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -47848,7 +47848,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>11:51:00</t>
+          <t>11:53:17</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -47916,7 +47916,7 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>11:51:00</t>
+          <t>11:53:17</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -47984,7 +47984,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>11:54:00</t>
+          <t>11:56:10</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -48052,7 +48052,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>11:54:00</t>
+          <t>11:56:10</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -48120,7 +48120,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>11:54:00</t>
+          <t>11:56:10</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -48188,7 +48188,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>11:54:00</t>
+          <t>11:56:10</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -48256,7 +48256,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>12:33:00</t>
+          <t>12:33:02</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -48324,7 +48324,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>12:33:00</t>
+          <t>12:33:02</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -48392,7 +48392,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>12:33:00</t>
+          <t>12:33:02</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -48460,7 +48460,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>12:33:00</t>
+          <t>12:33:02</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -48528,7 +48528,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>12:36:00</t>
+          <t>12:36:03</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -48596,7 +48596,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>12:36:00</t>
+          <t>12:36:03</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -48664,7 +48664,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>12:36:00</t>
+          <t>12:36:03</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -48732,7 +48732,7 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>12:36:00</t>
+          <t>12:36:03</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -49072,7 +49072,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>12:42:00</t>
+          <t>12:42:23</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -49140,7 +49140,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>12:42:00</t>
+          <t>12:42:23</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -49208,7 +49208,7 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>12:42:00</t>
+          <t>12:42:23</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -49276,7 +49276,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>12:42:00</t>
+          <t>12:42:23</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -49344,7 +49344,7 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>12:46:36</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -49412,7 +49412,7 @@
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>12:46:36</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
@@ -49480,7 +49480,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>12:46:36</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -49548,7 +49548,7 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>12:46:36</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
@@ -49616,7 +49616,7 @@
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>12:48:00</t>
+          <t>12:49:49</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
@@ -49684,7 +49684,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>12:48:00</t>
+          <t>12:49:49</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -49752,7 +49752,7 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>12:48:00</t>
+          <t>12:49:49</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -49820,7 +49820,7 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>12:48:00</t>
+          <t>12:49:49</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
@@ -49888,7 +49888,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>12:51:00</t>
+          <t>12:52:13</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -49956,7 +49956,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>12:51:00</t>
+          <t>12:52:13</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -50024,7 +50024,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>12:51:00</t>
+          <t>12:52:13</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -50092,7 +50092,7 @@
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>12:51:00</t>
+          <t>12:52:13</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
@@ -50160,7 +50160,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>12:54:00</t>
+          <t>12:55:09</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -50228,7 +50228,7 @@
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>12:54:00</t>
+          <t>12:55:09</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -50296,7 +50296,7 @@
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>12:54:00</t>
+          <t>12:55:09</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
@@ -50364,7 +50364,7 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>12:54:00</t>
+          <t>12:55:09</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -50432,7 +50432,7 @@
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>13:02:00</t>
+          <t>13:02:03</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -50500,7 +50500,7 @@
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>13:02:00</t>
+          <t>13:02:03</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -50568,7 +50568,7 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>13:02:00</t>
+          <t>13:02:03</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -50636,7 +50636,7 @@
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>13:02:00</t>
+          <t>13:02:03</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
@@ -50704,7 +50704,7 @@
       </c>
       <c r="H773" t="inlineStr">
         <is>
-          <t>13:05:00</t>
+          <t>13:07:47</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
@@ -50772,7 +50772,7 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>13:05:00</t>
+          <t>13:07:47</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -50840,7 +50840,7 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>13:05:00</t>
+          <t>13:07:47</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -50908,7 +50908,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>13:05:00</t>
+          <t>13:07:47</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -50976,7 +50976,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>13:08:00</t>
+          <t>13:13:55</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -51044,7 +51044,7 @@
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>13:08:00</t>
+          <t>13:13:55</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -51112,7 +51112,7 @@
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>13:08:00</t>
+          <t>13:13:55</t>
         </is>
       </c>
       <c r="I779" t="inlineStr">
@@ -51180,7 +51180,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>13:08:00</t>
+          <t>13:13:55</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -51248,7 +51248,7 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>13:11:00</t>
+          <t>13:18:13</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -51316,7 +51316,7 @@
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t>13:11:00</t>
+          <t>13:18:13</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
@@ -51384,7 +51384,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>13:11:00</t>
+          <t>13:18:13</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -51452,7 +51452,7 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>13:11:00</t>
+          <t>13:18:13</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
@@ -51520,7 +51520,7 @@
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>13:14:00</t>
+          <t>13:21:12</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
@@ -51588,7 +51588,7 @@
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>13:14:00</t>
+          <t>13:21:12</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
@@ -51656,7 +51656,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>13:14:00</t>
+          <t>13:21:12</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -51724,7 +51724,7 @@
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>13:14:00</t>
+          <t>13:21:12</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
@@ -51792,7 +51792,7 @@
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>13:17:00</t>
+          <t>13:24:20</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
@@ -51860,7 +51860,7 @@
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t>13:17:00</t>
+          <t>13:24:20</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
@@ -51928,7 +51928,7 @@
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t>13:17:00</t>
+          <t>13:24:20</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
@@ -51996,7 +51996,7 @@
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>13:17:00</t>
+          <t>13:24:20</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
@@ -52064,7 +52064,7 @@
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>13:20:00</t>
+          <t>13:29:28</t>
         </is>
       </c>
       <c r="I793" t="inlineStr">
@@ -52132,7 +52132,7 @@
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>13:20:00</t>
+          <t>13:29:28</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -52200,7 +52200,7 @@
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>13:20:00</t>
+          <t>13:29:28</t>
         </is>
       </c>
       <c r="I795" t="inlineStr">
@@ -52268,7 +52268,7 @@
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t>13:20:00</t>
+          <t>13:29:28</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -52336,7 +52336,7 @@
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>13:23:00</t>
+          <t>13:32:06</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
@@ -52404,7 +52404,7 @@
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>13:23:00</t>
+          <t>13:32:06</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -52472,7 +52472,7 @@
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t>13:23:00</t>
+          <t>13:32:06</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
@@ -52540,7 +52540,7 @@
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t>13:23:00</t>
+          <t>13:32:06</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -52608,7 +52608,7 @@
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>14:05:00</t>
+          <t>14:05:03</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
@@ -52676,7 +52676,7 @@
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>14:05:00</t>
+          <t>14:05:03</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
@@ -52744,7 +52744,7 @@
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>14:05:00</t>
+          <t>14:05:03</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
@@ -52812,7 +52812,7 @@
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t>14:05:00</t>
+          <t>14:05:03</t>
         </is>
       </c>
       <c r="I804" t="inlineStr">
@@ -52880,7 +52880,7 @@
       </c>
       <c r="H805" t="inlineStr">
         <is>
-          <t>14:09:00</t>
+          <t>14:09:24</t>
         </is>
       </c>
       <c r="I805" t="inlineStr">
@@ -52948,7 +52948,7 @@
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>14:09:00</t>
+          <t>14:09:24</t>
         </is>
       </c>
       <c r="I806" t="inlineStr">
@@ -53016,7 +53016,7 @@
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>14:09:00</t>
+          <t>14:09:24</t>
         </is>
       </c>
       <c r="I807" t="inlineStr">
@@ -53084,7 +53084,7 @@
       </c>
       <c r="H808" t="inlineStr">
         <is>
-          <t>14:09:00</t>
+          <t>14:09:24</t>
         </is>
       </c>
       <c r="I808" t="inlineStr">
@@ -53152,7 +53152,7 @@
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>14:14:00</t>
+          <t>14:13:59</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
@@ -53220,7 +53220,7 @@
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>14:14:00</t>
+          <t>14:13:59</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
@@ -53288,7 +53288,7 @@
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>14:14:00</t>
+          <t>14:13:59</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
@@ -53356,7 +53356,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>14:14:00</t>
+          <t>14:13:59</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -53424,7 +53424,7 @@
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>14:18:00</t>
+          <t>14:18:30</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
@@ -53492,7 +53492,7 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>14:18:00</t>
+          <t>14:18:30</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -53560,7 +53560,7 @@
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>14:18:00</t>
+          <t>14:18:30</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
@@ -53628,7 +53628,7 @@
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>14:18:00</t>
+          <t>14:18:30</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
@@ -53696,7 +53696,7 @@
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>14:27:00</t>
+          <t>14:27:12</t>
         </is>
       </c>
       <c r="I817" t="inlineStr">
@@ -53764,7 +53764,7 @@
       </c>
       <c r="H818" t="inlineStr">
         <is>
-          <t>14:27:00</t>
+          <t>14:27:12</t>
         </is>
       </c>
       <c r="I818" t="inlineStr">
@@ -53832,7 +53832,7 @@
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>14:27:00</t>
+          <t>14:27:12</t>
         </is>
       </c>
       <c r="I819" t="inlineStr">
@@ -53900,7 +53900,7 @@
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>14:27:00</t>
+          <t>14:27:12</t>
         </is>
       </c>
       <c r="I820" t="inlineStr">
@@ -53968,7 +53968,7 @@
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>14:31:00</t>
+          <t>14:31:44</t>
         </is>
       </c>
       <c r="I821" t="inlineStr">
@@ -54036,7 +54036,7 @@
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>14:31:00</t>
+          <t>14:31:44</t>
         </is>
       </c>
       <c r="I822" t="inlineStr">
@@ -54104,7 +54104,7 @@
       </c>
       <c r="H823" t="inlineStr">
         <is>
-          <t>14:31:00</t>
+          <t>14:31:44</t>
         </is>
       </c>
       <c r="I823" t="inlineStr">
@@ -54172,7 +54172,7 @@
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>14:31:00</t>
+          <t>14:31:44</t>
         </is>
       </c>
       <c r="I824" t="inlineStr">
@@ -54240,7 +54240,7 @@
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>14:36:00</t>
+          <t>14:44:56</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
@@ -54308,7 +54308,7 @@
       </c>
       <c r="H826" t="inlineStr">
         <is>
-          <t>14:36:00</t>
+          <t>14:44:56</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
@@ -54376,7 +54376,7 @@
       </c>
       <c r="H827" t="inlineStr">
         <is>
-          <t>14:36:00</t>
+          <t>14:44:56</t>
         </is>
       </c>
       <c r="I827" t="inlineStr">
@@ -54444,7 +54444,7 @@
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>14:36:00</t>
+          <t>14:44:56</t>
         </is>
       </c>
       <c r="I828" t="inlineStr">
@@ -54512,7 +54512,7 @@
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>14:40:00</t>
+          <t>14:48:18</t>
         </is>
       </c>
       <c r="I829" t="inlineStr">
@@ -54580,7 +54580,7 @@
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>14:40:00</t>
+          <t>14:48:18</t>
         </is>
       </c>
       <c r="I830" t="inlineStr">
@@ -54648,7 +54648,7 @@
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>14:40:00</t>
+          <t>14:48:18</t>
         </is>
       </c>
       <c r="I831" t="inlineStr">
@@ -54716,7 +54716,7 @@
       </c>
       <c r="H832" t="inlineStr">
         <is>
-          <t>14:40:00</t>
+          <t>14:48:18</t>
         </is>
       </c>
       <c r="I832" t="inlineStr">
@@ -54784,7 +54784,7 @@
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>14:49:00</t>
+          <t>14:56:25</t>
         </is>
       </c>
       <c r="I833" t="inlineStr">
@@ -54852,7 +54852,7 @@
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>14:49:00</t>
+          <t>14:56:25</t>
         </is>
       </c>
       <c r="I834" t="inlineStr">
@@ -54920,7 +54920,7 @@
       </c>
       <c r="H835" t="inlineStr">
         <is>
-          <t>14:49:00</t>
+          <t>14:56:25</t>
         </is>
       </c>
       <c r="I835" t="inlineStr">
@@ -54988,7 +54988,7 @@
       </c>
       <c r="H836" t="inlineStr">
         <is>
-          <t>14:49:00</t>
+          <t>14:56:25</t>
         </is>
       </c>
       <c r="I836" t="inlineStr">
@@ -55056,7 +55056,7 @@
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t>14:53:00</t>
+          <t>14:59:55</t>
         </is>
       </c>
       <c r="I837" t="inlineStr">
@@ -55124,7 +55124,7 @@
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t>14:53:00</t>
+          <t>14:59:55</t>
         </is>
       </c>
       <c r="I838" t="inlineStr">
@@ -55192,7 +55192,7 @@
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t>14:53:00</t>
+          <t>14:59:55</t>
         </is>
       </c>
       <c r="I839" t="inlineStr">
@@ -55260,7 +55260,7 @@
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>14:53:00</t>
+          <t>14:59:55</t>
         </is>
       </c>
       <c r="I840" t="inlineStr">
@@ -55328,7 +55328,7 @@
       </c>
       <c r="H841" t="inlineStr">
         <is>
-          <t>14:58:00</t>
+          <t>15:05:11</t>
         </is>
       </c>
       <c r="I841" t="inlineStr">
@@ -55396,7 +55396,7 @@
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t>14:58:00</t>
+          <t>15:05:11</t>
         </is>
       </c>
       <c r="I842" t="inlineStr">
@@ -55464,7 +55464,7 @@
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>14:58:00</t>
+          <t>15:05:11</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
@@ -55532,7 +55532,7 @@
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>14:58:00</t>
+          <t>15:05:11</t>
         </is>
       </c>
       <c r="I844" t="inlineStr">
@@ -55600,7 +55600,7 @@
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>15:02:00</t>
+          <t>15:10:58</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
@@ -55668,7 +55668,7 @@
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>15:02:00</t>
+          <t>15:10:58</t>
         </is>
       </c>
       <c r="I846" t="inlineStr">
@@ -55736,7 +55736,7 @@
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>15:02:00</t>
+          <t>15:10:58</t>
         </is>
       </c>
       <c r="I847" t="inlineStr">
@@ -55804,7 +55804,7 @@
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>15:02:00</t>
+          <t>15:10:58</t>
         </is>
       </c>
       <c r="I848" t="inlineStr">
@@ -55872,7 +55872,7 @@
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>15:11:00</t>
+          <t>15:19:27</t>
         </is>
       </c>
       <c r="I849" t="inlineStr">
@@ -55944,7 +55944,7 @@
       </c>
       <c r="H850" t="inlineStr">
         <is>
-          <t>15:11:00</t>
+          <t>15:19:27</t>
         </is>
       </c>
       <c r="I850" t="inlineStr">
@@ -56016,7 +56016,7 @@
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>15:11:00</t>
+          <t>15:19:27</t>
         </is>
       </c>
       <c r="I851" t="inlineStr">
@@ -56088,7 +56088,7 @@
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>15:11:00</t>
+          <t>15:19:27</t>
         </is>
       </c>
       <c r="I852" t="inlineStr">
@@ -56160,7 +56160,7 @@
       </c>
       <c r="H853" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>15:23:06</t>
         </is>
       </c>
       <c r="I853" t="inlineStr">
@@ -56232,7 +56232,7 @@
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>15:23:06</t>
         </is>
       </c>
       <c r="I854" t="inlineStr">
@@ -56304,7 +56304,7 @@
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>15:23:06</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
@@ -56376,7 +56376,7 @@
       </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>15:23:06</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
@@ -56448,7 +56448,7 @@
       </c>
       <c r="H857" t="inlineStr">
         <is>
-          <t>15:24:00</t>
+          <t>15:31:56</t>
         </is>
       </c>
       <c r="I857" t="inlineStr">
@@ -56520,7 +56520,7 @@
       </c>
       <c r="H858" t="inlineStr">
         <is>
-          <t>15:24:00</t>
+          <t>15:31:56</t>
         </is>
       </c>
       <c r="I858" t="inlineStr">
@@ -56592,7 +56592,7 @@
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t>15:24:00</t>
+          <t>15:31:56</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
@@ -56664,7 +56664,7 @@
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>15:24:00</t>
+          <t>15:31:56</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
@@ -56736,7 +56736,7 @@
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>15:32:00</t>
+          <t>15:36:44</t>
         </is>
       </c>
       <c r="I861" t="inlineStr">
@@ -56808,7 +56808,7 @@
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>15:32:00</t>
+          <t>15:36:44</t>
         </is>
       </c>
       <c r="I862" t="inlineStr">
@@ -56880,7 +56880,7 @@
       </c>
       <c r="H863" t="inlineStr">
         <is>
-          <t>15:32:00</t>
+          <t>15:36:44</t>
         </is>
       </c>
       <c r="I863" t="inlineStr">
@@ -56952,7 +56952,7 @@
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>15:32:00</t>
+          <t>15:36:44</t>
         </is>
       </c>
       <c r="I864" t="inlineStr">

--- a/events/Penrith_2025_WCH/Penrith_2025_WCH_start.xlsx
+++ b/events/Penrith_2025_WCH/Penrith_2025_WCH_start.xlsx
@@ -847,6 +847,11 @@
       <c r="K6" t="n">
         <v>5</v>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>NG Wee Meng</t>
@@ -910,6 +915,11 @@
       <c r="K7" t="n">
         <v>6</v>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>LIAO Li-Hong</t>
@@ -1162,6 +1172,11 @@
       <c r="K11" t="n">
         <v>10</v>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>LYU Luhui</t>
@@ -1225,6 +1240,11 @@
       <c r="K12" t="n">
         <v>11</v>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>WU Shao-Hsuan</t>
@@ -1288,6 +1308,11 @@
       <c r="K13" t="n">
         <v>12</v>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>GUBENKO Nikita</t>
@@ -1351,6 +1376,11 @@
       <c r="K14" t="n">
         <v>13</v>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>SMIRNOV Egor</t>
@@ -1414,6 +1444,11 @@
       <c r="K15" t="n">
         <v>14</v>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>SNOOK George</t>
@@ -1477,6 +1512,11 @@
       <c r="K16" t="n">
         <v>15</v>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>NIJHAWAN Nikhil</t>
@@ -1540,6 +1580,11 @@
       <c r="K17" t="n">
         <v>16</v>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>ZHANG Jiahao</t>
@@ -1603,6 +1648,11 @@
       <c r="K18" t="n">
         <v>17</v>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>GONSENICA Adam</t>
@@ -1666,6 +1716,11 @@
       <c r="K19" t="n">
         <v>18</v>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
           <t>PLAUDIS Martins</t>
@@ -1729,6 +1784,11 @@
       <c r="K20" t="n">
         <v>19</v>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>EIGEL Pavel</t>
@@ -1792,6 +1852,11 @@
       <c r="K21" t="n">
         <v>20</v>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>KOZLOV Ivan</t>
@@ -1855,6 +1920,11 @@
       <c r="K22" t="n">
         <v>21</v>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>TANAKA Yuuki</t>
@@ -1918,6 +1988,11 @@
       <c r="K23" t="n">
         <v>22</v>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>JACOB Lucas</t>
@@ -1981,6 +2056,11 @@
       <c r="K24" t="n">
         <v>23</v>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
           <t>MUTO Yusuke</t>
@@ -2044,6 +2124,11 @@
       <c r="K25" t="n">
         <v>24</v>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
           <t>REINOSO Antonio</t>
@@ -2107,6 +2192,11 @@
       <c r="K26" t="n">
         <v>25</v>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
           <t>MAPELLI Guilherme</t>
@@ -2170,6 +2260,11 @@
       <c r="K27" t="n">
         <v>26</v>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>UKALOVIC Thomas</t>
@@ -2233,6 +2328,11 @@
       <c r="K28" t="n">
         <v>27</v>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
           <t>SOVKO Serhii</t>
@@ -2296,6 +2396,11 @@
       <c r="K29" t="n">
         <v>28</v>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
           <t>BRZEZINSKI Jakub</t>
@@ -2359,6 +2464,11 @@
       <c r="K30" t="n">
         <v>29</v>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
           <t>CUNHA Joao</t>
@@ -2422,6 +2532,11 @@
       <c r="K31" t="n">
         <v>30</v>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
           <t>KREMSLEHNER Moritz</t>
@@ -2485,6 +2600,11 @@
       <c r="K32" t="n">
         <v>31</v>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr">
         <is>
           <t>BOYD Trevor</t>
@@ -2548,6 +2668,11 @@
       <c r="K33" t="n">
         <v>32</v>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
           <t>FRIEDENSON Kaelin</t>
@@ -2611,6 +2736,11 @@
       <c r="K34" t="n">
         <v>33</v>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
           <t>TRIPANO Manuel</t>
@@ -2674,6 +2804,11 @@
       <c r="K35" t="n">
         <v>34</v>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
           <t>LOCNIKAR Jan</t>
@@ -2737,6 +2872,11 @@
       <c r="K36" t="n">
         <v>35</v>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr">
         <is>
           <t>LEITNER Mario</t>
@@ -2800,6 +2940,11 @@
       <c r="K37" t="n">
         <v>36</v>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
           <t>ZIELONKA Mark</t>
@@ -2863,6 +3008,11 @@
       <c r="K38" t="n">
         <v>37</v>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr">
         <is>
           <t>ECHANIZ Pau</t>
@@ -2926,6 +3076,11 @@
       <c r="K39" t="n">
         <v>38</v>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
           <t>MCCREERY Alistair</t>
@@ -2989,6 +3144,11 @@
       <c r="K40" t="n">
         <v>39</v>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr">
         <is>
           <t>HUANG Liman</t>
@@ -3052,6 +3212,11 @@
       <c r="K41" t="n">
         <v>40</v>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr">
         <is>
           <t>RUDORFER Martin</t>
@@ -3115,6 +3280,11 @@
       <c r="K42" t="n">
         <v>41</v>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr">
         <is>
           <t>GRIGAR Jakub</t>
@@ -3178,6 +3348,11 @@
       <c r="K43" t="n">
         <v>42</v>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr">
         <is>
           <t>LONG Kyler James</t>
@@ -3241,6 +3416,11 @@
       <c r="K44" t="n">
         <v>43</v>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr">
         <is>
           <t>ALVARENGA Frederico</t>
@@ -3304,6 +3484,11 @@
       <c r="K45" t="n">
         <v>44</v>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr">
         <is>
           <t>HALCIN Martin</t>
@@ -3367,6 +3552,11 @@
       <c r="K46" t="n">
         <v>45</v>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr">
         <is>
           <t>FERRAZZI Xabier</t>
@@ -3430,6 +3620,11 @@
       <c r="K47" t="n">
         <v>46</v>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr">
         <is>
           <t>IVCHENKO Artem</t>
@@ -3493,6 +3688,11 @@
       <c r="K48" t="n">
         <v>47</v>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr">
         <is>
           <t>COLLIER Nicholas</t>
@@ -3556,6 +3756,11 @@
       <c r="K49" t="n">
         <v>48</v>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr">
         <is>
           <t>DESNOS Mathieu</t>
@@ -3619,6 +3824,11 @@
       <c r="K50" t="n">
         <v>49</v>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr">
         <is>
           <t>AUBERTIN Maxime</t>
@@ -3682,6 +3892,11 @@
       <c r="K51" t="n">
         <v>50</v>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr">
         <is>
           <t>CASTRYCK Titouan</t>
@@ -3745,6 +3960,11 @@
       <c r="K52" t="n">
         <v>51</v>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="R52" t="inlineStr">
         <is>
           <t>POPE Benjamin</t>
@@ -3808,6 +4028,11 @@
       <c r="K53" t="n">
         <v>52</v>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="R53" t="inlineStr">
         <is>
           <t>ANDERSON Timothy</t>
@@ -3871,6 +4096,11 @@
       <c r="K54" t="n">
         <v>53</v>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="R54" t="inlineStr">
         <is>
           <t>HENGST Stefan</t>
@@ -3934,6 +4164,11 @@
       <c r="K55" t="n">
         <v>54</v>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="R55" t="inlineStr">
         <is>
           <t>KUCHNO Tadeusz</t>
@@ -3997,6 +4232,11 @@
       <c r="K56" t="n">
         <v>55</v>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="R56" t="inlineStr">
         <is>
           <t>CHIARELLO Gelindo</t>
@@ -4060,6 +4300,11 @@
       <c r="K57" t="n">
         <v>56</v>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr">
         <is>
           <t>NOVAK Matyas</t>
@@ -4123,6 +4368,11 @@
       <c r="K58" t="n">
         <v>57</v>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="R58" t="inlineStr">
         <is>
           <t>ROELLER Tillmann</t>
@@ -4186,6 +4436,11 @@
       <c r="K59" t="n">
         <v>58</v>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="R59" t="inlineStr">
         <is>
           <t>DELFOUR Lucien</t>
@@ -4249,6 +4504,11 @@
       <c r="K60" t="n">
         <v>59</v>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R60" t="inlineStr">
         <is>
           <t>KREJCI Jakub</t>
@@ -4312,6 +4572,11 @@
       <c r="K61" t="n">
         <v>60</v>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="R61" t="inlineStr">
         <is>
           <t>DE COSTER Gabriel</t>
@@ -4375,6 +4640,11 @@
       <c r="K62" t="n">
         <v>61</v>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R62" t="inlineStr">
         <is>
           <t>BALDONI Alex</t>
@@ -4438,6 +4708,11 @@
       <c r="K63" t="n">
         <v>62</v>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R63" t="inlineStr">
         <is>
           <t>LEAVER Sam</t>
@@ -4501,6 +4776,11 @@
       <c r="K64" t="n">
         <v>63</v>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="R64" t="inlineStr">
         <is>
           <t>HOCEVAR Ziga Lin</t>
@@ -4564,6 +4844,11 @@
       <c r="K65" t="n">
         <v>64</v>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="R65" t="inlineStr">
         <is>
           <t>HEGGE Noah</t>
@@ -4627,6 +4912,11 @@
       <c r="K66" t="n">
         <v>65</v>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R66" t="inlineStr">
         <is>
           <t>ROHRER Jan</t>
@@ -4690,6 +4980,11 @@
       <c r="K67" t="n">
         <v>66</v>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="R67" t="inlineStr">
         <is>
           <t>ECHEVERRIA OLGUIN Andraz</t>
@@ -4753,6 +5048,11 @@
       <c r="K68" t="n">
         <v>67</v>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R68" t="inlineStr">
         <is>
           <t>DE GENNARO Giovanni</t>
@@ -4816,6 +5116,11 @@
       <c r="K69" t="n">
         <v>68</v>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="R69" t="inlineStr">
         <is>
           <t>GONCALVES Pedro</t>
@@ -4879,6 +5184,11 @@
       <c r="K70" t="n">
         <v>69</v>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="R70" t="inlineStr">
         <is>
           <t>RENIA Benjamin</t>
@@ -4942,6 +5252,11 @@
       <c r="K71" t="n">
         <v>70</v>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R71" t="inlineStr">
         <is>
           <t>DICKSON Jonny</t>
@@ -5005,6 +5320,11 @@
       <c r="K72" t="n">
         <v>71</v>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R72" t="inlineStr">
         <is>
           <t>MADORE Mathurin</t>
@@ -5068,6 +5388,11 @@
       <c r="K73" t="n">
         <v>72</v>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="R73" t="inlineStr">
         <is>
           <t>POLACZYK Mateusz</t>
@@ -5131,6 +5456,11 @@
       <c r="K74" t="n">
         <v>73</v>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R74" t="inlineStr">
         <is>
           <t>OCHOA Manuel</t>
@@ -5194,6 +5524,11 @@
       <c r="K75" t="n">
         <v>74</v>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R75" t="inlineStr">
         <is>
           <t>LLORENTE David</t>
@@ -5257,6 +5592,11 @@
       <c r="K76" t="n">
         <v>75</v>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="R76" t="inlineStr">
         <is>
           <t>DOUGOUD Martin</t>
@@ -5320,6 +5660,11 @@
       <c r="K77" t="n">
         <v>76</v>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="R77" t="inlineStr">
         <is>
           <t>BUTCHER Finn</t>
@@ -5383,6 +5728,11 @@
       <c r="K78" t="n">
         <v>77</v>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R78" t="inlineStr">
         <is>
           <t>CLARKE Joseph</t>
@@ -5446,6 +5796,11 @@
       <c r="K79" t="n">
         <v>78</v>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="R79" t="inlineStr">
         <is>
           <t>SOKOLOVA Mariia</t>
@@ -5509,6 +5864,11 @@
       <c r="K80" t="n">
         <v>79</v>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="R80" t="inlineStr">
         <is>
           <t>KURIA Michelle Wambui</t>
@@ -5572,6 +5932,11 @@
       <c r="K81" t="n">
         <v>80</v>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="R81" t="inlineStr">
         <is>
           <t>XHEMAJLJI Blandine</t>
@@ -5635,6 +6000,11 @@
       <c r="K82" t="n">
         <v>81</v>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="R82" t="inlineStr">
         <is>
           <t>CHANG Chu-Han</t>
@@ -5698,6 +6068,11 @@
       <c r="K83" t="n">
         <v>82</v>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="R83" t="inlineStr">
         <is>
           <t>MINAZOVA Alsu</t>
@@ -5761,6 +6136,11 @@
       <c r="K84" t="n">
         <v>83</v>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="R84" t="inlineStr">
         <is>
           <t>KRYLOVA Kseniia</t>
@@ -5824,6 +6204,11 @@
       <c r="K85" t="n">
         <v>84</v>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="R85" t="inlineStr">
         <is>
           <t>WU Ting-I</t>
@@ -5887,6 +6272,11 @@
       <c r="K86" t="n">
         <v>85</v>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="R86" t="inlineStr">
         <is>
           <t>MILLS Waris</t>
@@ -5950,6 +6340,11 @@
       <c r="K87" t="n">
         <v>86</v>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
       <c r="R87" t="inlineStr">
         <is>
           <t>YAZAWA Aki</t>
@@ -6013,6 +6408,11 @@
       <c r="K88" t="n">
         <v>87</v>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="R88" t="inlineStr">
         <is>
           <t>LUKNAROVA Emanuela</t>
@@ -6076,6 +6476,11 @@
       <c r="K89" t="n">
         <v>88</v>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="R89" t="inlineStr">
         <is>
           <t>PITCHER FARRELL Cleo</t>
@@ -6139,6 +6544,11 @@
       <c r="K90" t="n">
         <v>89</v>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="R90" t="inlineStr">
         <is>
           <t>WILLIAMS Courtney</t>
@@ -6202,6 +6612,11 @@
       <c r="K91" t="n">
         <v>90</v>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="R91" t="inlineStr">
         <is>
           <t>HILGERTOVA Amalie</t>
@@ -6265,6 +6680,11 @@
       <c r="K92" t="n">
         <v>91</v>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="R92" t="inlineStr">
         <is>
           <t>PLATA Laura</t>
@@ -6328,6 +6748,11 @@
       <c r="K93" t="n">
         <v>92</v>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="R93" t="inlineStr">
         <is>
           <t>REX Rosie</t>
@@ -6391,6 +6816,11 @@
       <c r="K94" t="n">
         <v>93</v>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="R94" t="inlineStr">
         <is>
           <t>GORA Aleksandra</t>
@@ -6454,6 +6884,11 @@
       <c r="K95" t="n">
         <v>94</v>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="R95" t="inlineStr">
         <is>
           <t>BRZESKA Dominika</t>
@@ -6517,6 +6952,11 @@
       <c r="K96" t="n">
         <v>95</v>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="R96" t="inlineStr">
         <is>
           <t>SORRIBES Laia</t>
@@ -6580,6 +7020,11 @@
       <c r="K97" t="n">
         <v>96</v>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="R97" t="inlineStr">
         <is>
           <t>O'CALLAGHAN Georgia</t>
@@ -6643,6 +7088,11 @@
       <c r="K98" t="n">
         <v>97</v>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="R98" t="inlineStr">
         <is>
           <t>DAVIDSON Codie</t>
@@ -6706,6 +7156,11 @@
       <c r="K99" t="n">
         <v>98</v>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="R99" t="inlineStr">
         <is>
           <t>STANOVSKA Sona</t>
@@ -6769,6 +7224,11 @@
       <c r="K100" t="n">
         <v>99</v>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="R100" t="inlineStr">
         <is>
           <t>PANKOVA Zuzana</t>
@@ -6832,6 +7292,11 @@
       <c r="K101" t="n">
         <v>100</v>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="R101" t="inlineStr">
         <is>
           <t>ALTMAN Marcella</t>
@@ -6895,6 +7360,11 @@
       <c r="K102" t="n">
         <v>101</v>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="R102" t="inlineStr">
         <is>
           <t>REINOSO Sofia</t>
@@ -6958,6 +7428,11 @@
       <c r="K103" t="n">
         <v>102</v>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="R103" t="inlineStr">
         <is>
           <t>US Viktoriia</t>
@@ -7021,6 +7496,11 @@
       <c r="K104" t="n">
         <v>103</v>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="R104" t="inlineStr">
         <is>
           <t>BAYN Nele</t>
@@ -7084,6 +7564,11 @@
       <c r="K105" t="n">
         <v>104</v>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R105" t="inlineStr">
         <is>
           <t>NOVAK Ajda</t>
@@ -7147,6 +7632,11 @@
       <c r="K106" t="n">
         <v>105</v>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="R106" t="inlineStr">
         <is>
           <t>TEUNISSEN Lena</t>
@@ -7210,6 +7700,11 @@
       <c r="K107" t="n">
         <v>106</v>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="R107" t="inlineStr">
         <is>
           <t>LI Shiting</t>
@@ -7273,6 +7768,11 @@
       <c r="K108" t="n">
         <v>107</v>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="R108" t="inlineStr">
         <is>
           <t>SAMKOVA Olga</t>
@@ -7336,6 +7836,11 @@
       <c r="K109" t="n">
         <v>108</v>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R109" t="inlineStr">
         <is>
           <t>HERZOG Andrea</t>
@@ -7399,6 +7904,11 @@
       <c r="K110" t="n">
         <v>109</v>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="R110" t="inlineStr">
         <is>
           <t>HOCEVAR Eva Alina</t>
@@ -7462,6 +7972,11 @@
       <c r="K111" t="n">
         <v>110</v>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="R111" t="inlineStr">
         <is>
           <t>SABATTINI Chiara</t>
@@ -7525,6 +8040,11 @@
       <c r="K112" t="n">
         <v>111</v>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="R112" t="inlineStr">
         <is>
           <t>LEAVER Lois</t>
@@ -7588,6 +8108,11 @@
       <c r="K113" t="n">
         <v>112</v>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R113" t="inlineStr">
         <is>
           <t>LAZKANO Miren</t>
@@ -7651,6 +8176,11 @@
       <c r="K114" t="n">
         <v>113</v>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R114" t="inlineStr">
         <is>
           <t>SATILA Ana</t>
@@ -7714,6 +8244,11 @@
       <c r="K115" t="n">
         <v>114</v>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="R115" t="inlineStr">
         <is>
           <t>DORIA Monica</t>
@@ -7777,6 +8312,11 @@
       <c r="K116" t="n">
         <v>115</v>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="R116" t="inlineStr">
         <is>
           <t>ESTACIA NETA Omira</t>
@@ -7840,6 +8380,11 @@
       <c r="K117" t="n">
         <v>116</v>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="R117" t="inlineStr">
         <is>
           <t>XIE Xueting</t>
@@ -7903,6 +8448,11 @@
       <c r="K118" t="n">
         <v>117</v>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R118" t="inlineStr">
         <is>
           <t>KNEBLOVA Tereza</t>
@@ -7966,6 +8516,11 @@
       <c r="K119" t="n">
         <v>118</v>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="R119" t="inlineStr">
         <is>
           <t>ZWOLINSKA Klaudia</t>
@@ -8029,6 +8584,11 @@
       <c r="K120" t="n">
         <v>119</v>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R120" t="inlineStr">
         <is>
           <t>SETCHELL Nikita</t>
@@ -8092,6 +8652,11 @@
       <c r="K121" t="n">
         <v>120</v>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R121" t="inlineStr">
         <is>
           <t>VUITTON Emma</t>
@@ -8155,6 +8720,11 @@
       <c r="K122" t="n">
         <v>121</v>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R122" t="inlineStr">
         <is>
           <t>LEIBFARTH Evy</t>
@@ -8218,6 +8788,11 @@
       <c r="K123" t="n">
         <v>122</v>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="R123" t="inlineStr">
         <is>
           <t>FUNK Ricarda</t>
@@ -8281,6 +8856,11 @@
       <c r="K124" t="n">
         <v>123</v>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R124" t="inlineStr">
         <is>
           <t>CHOURRAUT Maialen</t>
@@ -8344,6 +8924,11 @@
       <c r="K125" t="n">
         <v>124</v>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R125" t="inlineStr">
         <is>
           <t>MARX Alena</t>
@@ -8407,6 +8992,11 @@
       <c r="K126" t="n">
         <v>125</v>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R126" t="inlineStr">
         <is>
           <t>FOX Noemie</t>
@@ -8470,6 +9060,11 @@
       <c r="K127" t="n">
         <v>126</v>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="R127" t="inlineStr">
         <is>
           <t>PRIGENT Camille</t>
@@ -8533,6 +9128,11 @@
       <c r="K128" t="n">
         <v>127</v>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R128" t="inlineStr">
         <is>
           <t>HUG Angele</t>
@@ -8595,6 +9195,11 @@
       </c>
       <c r="K129" t="n">
         <v>128</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
